--- a/data-manipulation-scripts/sheets-cleanup/sheets/CAPA BANCO- 26_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/CAPA BANCO- 26_01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="46">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -58,13 +58,13 @@
     <t>CAPA BANCO VERMELHA RRMOTOS POP110 2019 A 2022</t>
   </si>
   <si>
-    <t>CAPA BANCO RRMOTOS CAPA BANCOX250 TWISTER</t>
+    <t>CAPA BANCO RRMOTOS CBX250 TWISTER</t>
   </si>
   <si>
     <t>7898601381665</t>
   </si>
   <si>
-    <t>CAPA BANCO STILUS PCX 2016 EM DIANTE</t>
+    <t>CAPA BANCO STYLUS PCX 2016 EM DIANTE</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -76,7 +76,7 @@
     <t>7898601380163</t>
   </si>
   <si>
-    <t>CAPA BANCO STILUS BROS NXR 2009 A 2014</t>
+    <t>CAPA BANCO STYLUS BROS NXR 2009 A 2014</t>
   </si>
   <si>
     <t>7908664920708</t>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t>7898687690217</t>
+  </si>
+  <si>
+    <t>CAPA BANCO RRMOTOS CAPA BANCO CBX250 TWISTER</t>
   </si>
   <si>
     <t>7898601380736</t>
@@ -140,6 +143,12 @@
   </si>
   <si>
     <t xml:space="preserve">CAPA BANCO BAHIA </t>
+  </si>
+  <si>
+    <t>7899738015256</t>
+  </si>
+  <si>
+    <t>CAPA BANCO PIRACAPAS AZUL PCX150 2016 A 2021</t>
   </si>
 </sst>
 </file>
@@ -449,7 +458,9 @@
       <c r="C2" s="2">
         <v>4.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="2">
+        <v>38.0</v>
+      </c>
       <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
@@ -462,7 +473,9 @@
       <c r="C3" s="2">
         <v>2.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="2">
+        <v>38.0</v>
+      </c>
       <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
@@ -475,7 +488,9 @@
       <c r="C4" s="2">
         <v>5.0</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="2">
+        <v>30.0</v>
+      </c>
       <c r="E4" s="3" t="s">
         <v>6</v>
       </c>
@@ -488,7 +503,9 @@
       <c r="C5" s="2">
         <v>8.0</v>
       </c>
-      <c r="D5" s="5"/>
+      <c r="D5" s="2">
+        <v>30.0</v>
+      </c>
       <c r="E5" s="3" t="s">
         <v>6</v>
       </c>
@@ -501,7 +518,9 @@
       <c r="C6" s="2">
         <v>1.0</v>
       </c>
-      <c r="D6" s="5"/>
+      <c r="D6" s="2">
+        <v>32.0</v>
+      </c>
       <c r="E6" s="3" t="s">
         <v>6</v>
       </c>
@@ -514,7 +533,9 @@
       <c r="C7" s="2">
         <v>1.0</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="D7" s="2">
+        <v>32.0</v>
+      </c>
       <c r="E7" s="3" t="s">
         <v>6</v>
       </c>
@@ -527,7 +548,9 @@
       <c r="C8" s="2">
         <v>1.0</v>
       </c>
-      <c r="D8" s="5"/>
+      <c r="D8" s="2">
+        <v>30.0</v>
+      </c>
       <c r="E8" s="3" t="s">
         <v>6</v>
       </c>
@@ -540,7 +563,9 @@
       <c r="C9" s="2">
         <v>1.0</v>
       </c>
-      <c r="D9" s="5"/>
+      <c r="D9" s="2">
+        <v>30.0</v>
+      </c>
       <c r="E9" s="3" t="s">
         <v>6</v>
       </c>
@@ -553,20 +578,24 @@
       <c r="C10" s="2">
         <v>1.0</v>
       </c>
-      <c r="D10" s="5"/>
+      <c r="D10" s="2">
+        <v>42.0</v>
+      </c>
       <c r="E10" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4"/>
+      <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="2">
         <v>1.0</v>
       </c>
-      <c r="D11" s="5"/>
+      <c r="D11" s="2">
+        <v>42.0</v>
+      </c>
       <c r="E11" s="3" t="s">
         <v>6</v>
       </c>
@@ -581,7 +610,9 @@
       <c r="C12" s="2">
         <v>1.0</v>
       </c>
-      <c r="D12" s="5"/>
+      <c r="D12" s="2">
+        <v>45.0</v>
+      </c>
       <c r="E12" s="3" t="s">
         <v>6</v>
       </c>
@@ -596,7 +627,9 @@
       <c r="C13" s="2">
         <v>1.0</v>
       </c>
-      <c r="D13" s="5"/>
+      <c r="D13" s="2">
+        <v>30.0</v>
+      </c>
       <c r="E13" s="3" t="s">
         <v>6</v>
       </c>
@@ -611,7 +644,9 @@
       <c r="C14" s="2">
         <v>3.0</v>
       </c>
-      <c r="D14" s="5"/>
+      <c r="D14" s="2">
+        <v>40.0</v>
+      </c>
       <c r="E14" s="3" t="s">
         <v>6</v>
       </c>
@@ -638,42 +673,48 @@
         <v>24</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C16" s="2">
         <v>1.0</v>
       </c>
-      <c r="D16" s="5"/>
+      <c r="D16" s="2">
+        <v>40.0</v>
+      </c>
       <c r="E16" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" s="2">
         <v>3.0</v>
       </c>
-      <c r="D17" s="5"/>
+      <c r="D17" s="2">
+        <v>32.0</v>
+      </c>
       <c r="E17" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C18" s="2">
         <v>1.0</v>
       </c>
-      <c r="D18" s="5"/>
+      <c r="D18" s="2">
+        <v>30.0</v>
+      </c>
       <c r="E18" s="3" t="s">
         <v>6</v>
       </c>
@@ -681,67 +722,75 @@
     <row r="19">
       <c r="A19" s="4"/>
       <c r="B19" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19" s="2">
         <v>1.0</v>
       </c>
-      <c r="D19" s="5"/>
+      <c r="D19" s="2">
+        <v>30.0</v>
+      </c>
       <c r="E19" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C20" s="2">
         <v>1.0</v>
       </c>
-      <c r="D20" s="5"/>
+      <c r="D20" s="2">
+        <v>30.0</v>
+      </c>
       <c r="E20" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C21" s="2">
         <v>1.0</v>
       </c>
-      <c r="D21" s="5"/>
+      <c r="D21" s="2">
+        <v>40.0</v>
+      </c>
       <c r="E21" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C22" s="2">
         <v>3.0</v>
       </c>
-      <c r="D22" s="5"/>
+      <c r="D22" s="2">
+        <v>40.0</v>
+      </c>
       <c r="E22" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C23" s="2">
         <v>2.0</v>
@@ -758,12 +807,14 @@
         <v>18</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C24" s="2">
         <v>2.0</v>
       </c>
-      <c r="D24" s="5"/>
+      <c r="D24" s="2">
+        <v>29.0</v>
+      </c>
       <c r="E24" s="3" t="s">
         <v>6</v>
       </c>
@@ -771,27 +822,31 @@
     <row r="25">
       <c r="A25" s="4"/>
       <c r="B25" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C25" s="2">
         <v>1.0</v>
       </c>
-      <c r="D25" s="5"/>
+      <c r="D25" s="2">
+        <v>36.0</v>
+      </c>
       <c r="E25" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C26" s="2">
         <v>1.0</v>
       </c>
-      <c r="D26" s="5"/>
+      <c r="D26" s="2">
+        <v>30.0</v>
+      </c>
       <c r="E26" s="3" t="s">
         <v>6</v>
       </c>
@@ -799,21 +854,34 @@
     <row r="27">
       <c r="A27" s="4"/>
       <c r="B27" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>45.0</v>
+      </c>
       <c r="E27" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4"/>
+      <c r="A28" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="B28" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>75.0</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4"/>
